--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486950_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486950_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9862</v>
+        <v>5.2682</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8301</v>
+        <v>3.7697</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1561</v>
+        <v>1.4984</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7142</v>
+        <v>4.5388</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6877</v>
+        <v>0.8922</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0265</v>
+        <v>3.6466</v>
       </c>
       <c r="J2" t="n">
-        <v>2.647</v>
+        <v>5.5405</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7393</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9077</v>
+        <v>4.7355</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9328</v>
+        <v>-1.0017</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0516</v>
+        <v>0.0873</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1188</v>
+        <v>-1.089</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4641</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4641</v>
+        <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2042</v>
+        <v>0.9347</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4008</v>
+        <v>0.2827</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8034</v>
+        <v>0.652</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3963</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2177</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2246</v>
+        <v>5.1521</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6966</v>
+        <v>4.2035</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5281</v>
+        <v>0.9486</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5388</v>
+        <v>1.7142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8922</v>
+        <v>0.6877</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6466</v>
+        <v>1.0265</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5405</v>
+        <v>2.647</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8048999999999999</v>
+        <v>1.7393</v>
       </c>
       <c r="L3" t="n">
-        <v>4.7355</v>
+        <v>0.9077</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0017</v>
+        <v>-0.9328</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0873</v>
+        <v>-1.0516</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.089</v>
+        <v>0.1188</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2053</v>
+        <v>2.4641</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1088</v>
+        <v>2.3701</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7905</v>
+        <v>1.7742</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6816</v>
+        <v>0.5959</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.3963</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.2177</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7167</v>
+        <v>4.0179</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0161</v>
+        <v>1.0183</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7328</v>
+        <v>2.9996</v>
       </c>
       <c r="G4" t="n">
         <v>2.4071</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9225</v>
+        <v>0.3788</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4457</v>
+        <v>0.5888</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4768</v>
+        <v>-0.21</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6052</v>
+        <v>2.8681</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7752</v>
+        <v>1.364</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8301</v>
+        <v>1.504</v>
       </c>
       <c r="G5" t="n">
         <v>0.8156</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.763</v>
+        <v>1.0258</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1899</v>
+        <v>0.399</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9529</v>
+        <v>0.6268</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2433</v>
+        <v>-0.0228</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4728</v>
+        <v>-1.7982</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7161</v>
+        <v>1.7754</v>
       </c>
       <c r="G6" t="n">
         <v>-1.617</v>
@@ -922,13 +922,13 @@
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2443</v>
+        <v>0.9782</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0536</v>
+        <v>0.7282</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1908</v>
+        <v>0.2501</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2562</v>
+        <v>-0.5875</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1537</v>
+        <v>-0.6036</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1025</v>
+        <v>0.0161</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1837</v>
@@ -1000,13 +1000,13 @@
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.169</v>
+        <v>0.4997</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3489</v>
+        <v>0.2013</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1799</v>
+        <v>0.2985</v>
       </c>
       <c r="V7" t="n">
         <v>0.4805</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6029</v>
+        <v>-1.4184</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3573</v>
+        <v>-1.2914</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2455</v>
+        <v>-0.127</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0344</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6369</v>
+        <v>0.8214</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4416</v>
+        <v>0.5075</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1953</v>
+        <v>0.3139</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6562</v>
+        <v>-2.7381</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3067</v>
+        <v>-4.35</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6505</v>
+        <v>1.6119</v>
       </c>
       <c r="G9" t="n">
-        <v>0.322</v>
+        <v>-2.7718</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5901999999999999</v>
+        <v>-2.1637</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2682</v>
+        <v>-0.6081</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1373</v>
+        <v>-2.6567</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0584</v>
+        <v>-1.7222</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0789</v>
+        <v>-0.9345</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1846</v>
+        <v>-0.1151</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5318000000000001</v>
+        <v>-0.4415</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3472</v>
+        <v>0.3264</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.3122</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.1336</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6832</v>
+        <v>0.1569</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4493</v>
+        <v>0.3602</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2338</v>
+        <v>-0.2033</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3491</v>
+        <v>0.6982</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5893</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6919</v>
+        <v>-2.8883</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1269</v>
+        <v>-4.7975</v>
       </c>
       <c r="F10" t="n">
-        <v>1.435</v>
+        <v>1.9093</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6507</v>
@@ -1234,13 +1234,13 @@
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0409</v>
+        <v>0.8445</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7242</v>
+        <v>1.0536</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6833</v>
+        <v>-0.209</v>
       </c>
       <c r="V10" t="n">
         <v>0.4805</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9644</v>
+        <v>-3.3997</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2798</v>
+        <v>-4.2795</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3154</v>
+        <v>0.8798</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7718</v>
+        <v>0.322</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1637</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6081</v>
+        <v>-0.2682</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6567</v>
+        <v>0.1373</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7222</v>
+        <v>0.0584</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9345</v>
+        <v>0.0789</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1151</v>
+        <v>0.1846</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4415</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3264</v>
+        <v>-0.3472</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8214</v>
+        <v>-4.3122</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0534</v>
+        <v>-5.1336</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0694</v>
+        <v>0.9396</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5697</v>
+        <v>0.4765</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4997</v>
+        <v>0.4631</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6982</v>
+        <v>-0.3491</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6982</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.604399999999998</v>
+        <v>6.251499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.4114</v>
+        <v>-6.764700000000001</v>
       </c>
       <c r="F12" t="n">
         <v>13.0161</v>
@@ -1360,16 +1360,16 @@
         <v>-1.5251</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9347999999999997</v>
+        <v>-0.9347999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1.280799999999998</v>
+        <v>1.280799999999999</v>
       </c>
       <c r="K12" t="n">
         <v>1.0738</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2070999999999995</v>
+        <v>0.2070999999999996</v>
       </c>
       <c r="M12" t="n">
         <v>-3.7409</v>
@@ -1390,19 +1390,19 @@
         <v>16.4274</v>
       </c>
       <c r="S12" t="n">
-        <v>7.302800000000001</v>
+        <v>8.9497</v>
       </c>
       <c r="T12" t="n">
-        <v>4.7248</v>
+        <v>6.372</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5779</v>
+        <v>2.578</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2648</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9835</v>
+        <v>0.9834999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-2.2483</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7794</v>
+        <v>2.8126</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5512</v>
+        <v>1.2373</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2282</v>
+        <v>1.5752</v>
       </c>
       <c r="G13" t="n">
         <v>3.66</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8807</v>
+        <v>-0.8475</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4802</v>
+        <v>0.1664</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3609</v>
+        <v>-1.0139</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1574</v>
+        <v>2.0789</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6241</v>
+        <v>0.4149</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5332</v>
+        <v>1.664</v>
       </c>
       <c r="G14" t="n">
         <v>2.5583</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2151</v>
+        <v>0.1366</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0931</v>
+        <v>-0.3023</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3082</v>
+        <v>0.4389</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2019</v>
+        <v>1.568</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5849</v>
+        <v>-1.0619</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7868</v>
+        <v>2.6299</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2845</v>
@@ -1624,13 +1624,13 @@
         <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0885</v>
+        <v>-0.7225</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9222</v>
+        <v>-0.3992</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1663</v>
+        <v>-0.3233</v>
       </c>
       <c r="V15" t="n">
         <v>2.575</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8077</v>
+        <v>0.9507</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2369</v>
+        <v>0.9231</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4292</v>
+        <v>0.0276</v>
       </c>
       <c r="G16" t="n">
         <v>0.8915</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3425</v>
+        <v>-0.1995</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.159</v>
+        <v>-0.4728</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1836</v>
+        <v>0.2732</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6127</v>
+        <v>0.0566</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6596</v>
+        <v>-1.2872</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2724</v>
+        <v>1.3438</v>
       </c>
       <c r="G17" t="n">
         <v>-1.376</v>
@@ -1780,13 +1780,13 @@
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5513</v>
+        <v>-0.0049</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5461</v>
+        <v>-0.0815</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0052</v>
+        <v>0.0766</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3408</v>
+        <v>-0.6783</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.653</v>
+        <v>-1.13</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3122</v>
+        <v>0.4517</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5384</v>
@@ -1858,13 +1858,13 @@
         <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0344</v>
+        <v>-0.372</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5192</v>
+        <v>0.0038</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5152</v>
+        <v>-0.3757</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.369</v>
+        <v>-0.8347</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7878</v>
+        <v>-2.6346</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4188</v>
+        <v>1.7999</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0218</v>
+        <v>0.8992</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8174</v>
+        <v>-0.6323</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8392</v>
+        <v>1.5315</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8733</v>
+        <v>1.2082</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8234</v>
+        <v>-0.528</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6967</v>
+        <v>1.7361</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1485</v>
+        <v>-0.309</v>
       </c>
       <c r="N19" t="n">
-        <v>0.006</v>
+        <v>-0.1044</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1425</v>
+        <v>-0.2046</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8481</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6962</v>
+        <v>-4.5175</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8918</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5542</v>
+        <v>-0.5039</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3376</v>
+        <v>-0.1498</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5893</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6559</v>
+        <v>-1.2539</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9484</v>
+        <v>-2.8924</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2926</v>
+        <v>1.6384</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8992</v>
+        <v>1.0218</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6323</v>
+        <v>-0.8174</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5315</v>
+        <v>1.8392</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2082</v>
+        <v>0.8733</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.528</v>
+        <v>-0.8234</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7361</v>
+        <v>1.6967</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.309</v>
+        <v>0.1485</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1044</v>
+        <v>0.006</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2046</v>
+        <v>0.1425</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2588</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.5175</v>
+        <v>-3.6962</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4749</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8177</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6572</v>
+        <v>-0.1179</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>0.3491</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4203</v>
+        <v>-1.9583</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2215</v>
+        <v>-1.9077</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1988</v>
+        <v>-0.0506</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5276999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6175</v>
+        <v>-1.1555</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5851</v>
+        <v>-0.2713</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0324</v>
+        <v>-0.8842</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4805</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3778</v>
+        <v>-5.254</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.573</v>
+        <v>-4.6776</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8048</v>
+        <v>-0.5764</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8442</v>
@@ -2170,13 +2170,13 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7389</v>
+        <v>-0.6151</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0464</v>
+        <v>-0.0582</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7853</v>
+        <v>-0.5569</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.604699999999999</v>
+        <v>-2.512399999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-13.016</v>
+        <v>-13.0161</v>
       </c>
       <c r="F23" t="n">
-        <v>8.411399999999999</v>
+        <v>10.5035</v>
       </c>
       <c r="G23" t="n">
         <v>2.460000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>15.4007</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.3028</v>
+        <v>-5.2108</v>
       </c>
       <c r="T23" t="n">
         <v>-2.5778</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.7251</v>
+        <v>-2.633</v>
       </c>
       <c r="V23" t="n">
         <v>1.265</v>
